--- a/Tools/E2E_win64/Excel/Equipment.xlsx
+++ b/Tools/E2E_win64/Excel/Equipment.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\Project\Unity\GraduationProject\Tools\E2E_win64\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAEC8ED-42E4-4CBC-B9ED-595919E77A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C8D4B7-A074-448C-A41D-EBBEA95420F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E10D22D8-D959-4791-BF2F-99759CC50C36}"/>
+    <workbookView xWindow="8730" yWindow="3000" windowWidth="28800" windowHeight="15345" xr2:uid="{E10D22D8-D959-4791-BF2F-99759CC50C36}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponData1" sheetId="1" r:id="rId1"/>
-    <sheet name="WeaponData2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,14 +72,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ATK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dictance</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -90,26 +81,6 @@
   </si>
   <si>
     <t>M416</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是一把枪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是一柄长矛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是一把斧头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AXE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spear</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -518,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
@@ -552,16 +523,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -569,7 +540,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>3</v>
@@ -580,7 +551,7 @@
         <v>1001</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -592,7 +563,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -600,7 +571,7 @@
         <v>1002</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -612,7 +583,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -620,7 +591,7 @@
         <v>1003</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -632,140 +603,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9045A5-6F23-41ED-B7F1-845BA7CFDB87}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1001</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
-      <c r="E5">
-        <v>0.5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1002</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1000</v>
-      </c>
-      <c r="E6">
-        <v>0.05</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1003</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7">
-        <v>30</v>
-      </c>
-      <c r="D7">
-        <v>200</v>
-      </c>
-      <c r="E7">
-        <v>0.5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
